--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_ZALGIRIS KAUNAS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_ZALGIRIS KAUNAS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA40"/>
+  <dimension ref="A1:BA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.3127572016460906</v>
       </c>
       <c r="J2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>37</v>
@@ -752,13 +752,13 @@
         <v>0.8773584905660378</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8163265306122449</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8979591836734694</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
         <v>1.727272727272727</v>
@@ -801,13 +801,13 @@
         <v>0.3127572016460906</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>9.25</v>
@@ -882,13 +882,13 @@
         <v>0.8773584905660378</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8163265306122449</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8979591836734694</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
         <v>1.727272727272727</v>
@@ -931,13 +931,13 @@
         <v>0.1692307692307692</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>47</v>
@@ -1012,13 +1012,13 @@
         <v>1.275862068965517</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.196078431372549</v>
+        <v>0.0392156862745098</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>1.408163265306122</v>
@@ -1061,13 +1061,13 @@
         <v>0.1692307692307692</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>15.25</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>11.75</v>
@@ -1142,13 +1142,13 @@
         <v>1.275862068965517</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.196078431372549</v>
+        <v>0.0392156862745098</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>1.408163265306122</v>
@@ -1486,16 +1486,16 @@
         <v>52</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>16</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>235:32</t>
+          <t>120:31</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>8.429</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.111</v>
+        <v>0.217</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.022</v>
+        <v>0.043</v>
       </c>
       <c r="BA8" t="n">
         <v>0.222</v>
@@ -1651,16 +1651,16 @@
         <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>24</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>238:52</t>
+          <t>133:52</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>10.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.149</v>
+        <v>0.266</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.066</v>
+        <v>0.117</v>
       </c>
       <c r="BA9" t="n">
         <v>0.337</v>
@@ -1816,16 +1816,16 @@
         <v>68</v>
       </c>
       <c r="U10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>27</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>232:06</t>
+          <t>112:06</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>4.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.106</v>
+        <v>0.219</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.036</v>
+        <v>0.075</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.079</v>
+        <v>0.164</v>
       </c>
       <c r="BA10" t="n">
         <v>0.023</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>39:38</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.075</v>
+        <v>0.31</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>43:18</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,7 +2235,7 @@
         <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.046</v>
+        <v>0.15</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -2311,16 +2311,16 @@
         <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
         <v>31</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>242:09</t>
+          <t>127:09</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2400,13 +2400,13 @@
         <v>16.333</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.115</v>
+        <v>0.219</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.03</v>
+        <v>0.056</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.059</v>
+        <v>0.113</v>
       </c>
       <c r="BA13" t="n">
         <v>0.037</v>
@@ -2476,7 +2476,7 @@
         <v>5</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>98:58</t>
+          <t>58:57</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>5.667</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.089</v>
+        <v>0.15</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.026</v>
+        <v>0.044</v>
       </c>
       <c r="BA14" t="n">
         <v>0.038</v>
@@ -2644,13 +2644,13 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>5</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>127:50</t>
+          <t>62:48</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>5</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.074</v>
+        <v>0.151</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.037</v>
+        <v>0.076</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.041</v>
+        <v>0.083</v>
       </c>
       <c r="BA15" t="n">
         <v>0.019</v>
@@ -2806,10 +2806,10 @@
         <v>16</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>29:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.134</v>
+        <v>0.204</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.164</v>
+        <v>0.248</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.09</v>
+        <v>0.136</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>166:26</t>
+          <t>76:28</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>8</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.039</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.036</v>
+        <v>0.078</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.047</v>
+        <v>0.103</v>
       </c>
       <c r="BA17" t="n">
         <v>0.065</v>
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.143</v>
+        <v>0.274</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.057</v>
+        <v>0.11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.125</v>
+        <v>0.24</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -3301,16 +3301,16 @@
         <v>40</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>13</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>175:07</t>
+          <t>80:04</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.066</v>
+        <v>0.145</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.03</v>
+        <v>0.065</v>
       </c>
       <c r="BA19" t="n">
         <v>0.051</v>
@@ -3570,65 +3570,65 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="T21" t="n">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -3637,96 +3637,96 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>0.839</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>825:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>5</v>
+        <v>331.88</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>0.508</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>0.973</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.727</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>5.523</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3735,44 +3735,44 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="D22" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E22" t="n">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="H22" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="I22" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="J22" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K22" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="L22" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="N22" t="n">
         <v>26</v>
@@ -3781,76 +3781,76 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="R22" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="S22" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="T22" t="n">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="U22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="Z22" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.839</v>
+        <v>0.848</v>
       </c>
       <c r="AB22" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="AC22" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.444</v>
+        <v>0.413</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.231</v>
+        <v>0.176</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.25</v>
+        <v>0.714</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.298</v>
+        <v>0.37</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -3858,40 +3858,40 @@
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>331.88</v>
+        <v>334.96</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.508</v>
+        <v>0.583</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.973</v>
+        <v>1.036</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.133</v>
+        <v>0.146</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.313</v>
+        <v>0.169</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.727</v>
+        <v>1.408</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.523</v>
+        <v>5.306</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.25</v>
+        <v>6.714</v>
       </c>
       <c r="AX22" t="n">
         <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.119</v>
+        <v>0.129</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3900,436 +3900,436 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" t="n">
-        <v>347</v>
-      </c>
-      <c r="D23" t="n">
-        <v>96</v>
-      </c>
-      <c r="E23" t="n">
-        <v>173</v>
-      </c>
-      <c r="F23" t="n">
-        <v>37</v>
-      </c>
-      <c r="G23" t="n">
-        <v>87</v>
-      </c>
-      <c r="H23" t="n">
-        <v>44</v>
-      </c>
-      <c r="I23" t="n">
-        <v>59</v>
-      </c>
-      <c r="J23" t="n">
-        <v>69</v>
-      </c>
-      <c r="K23" t="n">
-        <v>89</v>
-      </c>
-      <c r="L23" t="n">
-        <v>51</v>
-      </c>
-      <c r="M23" t="n">
-        <v>14</v>
-      </c>
-      <c r="N23" t="n">
-        <v>26</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>47</v>
-      </c>
-      <c r="R23" t="n">
-        <v>81</v>
-      </c>
-      <c r="S23" t="n">
-        <v>80</v>
-      </c>
-      <c r="T23" t="n">
-        <v>404</v>
-      </c>
-      <c r="U23" t="n">
-        <v>22</v>
-      </c>
-      <c r="V23" t="n">
-        <v>61</v>
-      </c>
-      <c r="W23" t="n">
-        <v>20</v>
-      </c>
-      <c r="X23" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>106</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>125</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>73</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>825:00</t>
-        </is>
-      </c>
-      <c r="AO23" t="n">
-        <v>334.96</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.408</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>5.306</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>6.714</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
+          <t>#1 N. WILLIAMS-GOSS (Per Game)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>13</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>52</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>30:07</t>
+        </is>
+      </c>
+      <c r="AO24" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.857</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>5.571</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>8.429</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.222</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#1 N. WILLIAMS-GOSS (Per Game)</t>
+          <t>#3 S. FRANCISCO (Per Game)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>15.25</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="K25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>2.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="T25" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC25" t="n">
         <v>1.5</v>
       </c>
-      <c r="V25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AD25" t="n">
-        <v>0.667</v>
+        <v>0.167</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.5</v>
+        <v>8.25</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.3</v>
+        <v>0.303</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>58:53</t>
+          <t>33:28</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>13.15</v>
+        <v>17.89</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.513</v>
+        <v>0.396</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.989</v>
+        <v>0.852</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.133</v>
+        <v>0.112</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.308</v>
+        <v>0.358</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.857</v>
+        <v>3.875</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.571</v>
+        <v>6.625</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.429</v>
+        <v>10.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.111</v>
+        <v>0.266</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.015</v>
+        <v>0.036</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.022</v>
+        <v>0.117</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.222</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#3 S. FRANCISCO (Per Game)</t>
+          <t>#7 M. WRIGHT (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>15.25</v>
+        <v>13.75</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>4.5</v>
+        <v>7.25</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="G26" t="n">
-        <v>8.75</v>
+        <v>1.25</v>
       </c>
       <c r="H26" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>4.25</v>
       </c>
       <c r="J26" t="n">
-        <v>7.75</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="M26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N26" t="n">
         <v>1.25</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4347,279 +4347,279 @@
         <v>4.75</v>
       </c>
       <c r="T26" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.889</v>
+        <v>0.844</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
         <v>1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.167</v>
+        <v>0.667</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="AL26" t="n">
-        <v>8.25</v>
+        <v>1.25</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.303</v>
+        <v>0.2</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>59:43</t>
+          <t>28:01</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>17.89</v>
+        <v>12.37</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.396</v>
+        <v>0.632</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.48</v>
+        <v>0.663</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.852</v>
+        <v>1.112</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.112</v>
+        <v>0.162</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.358</v>
+        <v>0.353</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.875</v>
+        <v>0.25</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.625</v>
+        <v>4.25</v>
       </c>
       <c r="AW26" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.149</v>
+        <v>0.219</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.02</v>
+        <v>0.075</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.066</v>
+        <v>0.164</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.337</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#7 M. WRIGHT (Per Game)</t>
+          <t>#8 I. BRAZDEIKIS (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>13.75</v>
+        <v>0.5</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="E27" t="n">
-        <v>7.25</v>
+        <v>0.25</v>
       </c>
       <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>0.25</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="Z27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>02:24</t>
+        </is>
+      </c>
+      <c r="AO27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AS27" t="n">
         <v>0.5</v>
       </c>
-      <c r="K27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>68</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>58:01</t>
-        </is>
-      </c>
-      <c r="AO27" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.663</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.112</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.162</v>
-      </c>
       <c r="AT27" t="n">
-        <v>0.353</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.25</v>
+        <v>1</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.106</v>
+        <v>0.31</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#8 I. BRAZDEIKIS (Per Game)</t>
+          <t>#9 D. GIEDRAITIS (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -4665,19 +4665,19 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -4692,31 +4692,31 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
         <v>0.25</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AF28" t="n">
         <v>0.25</v>
       </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
@@ -4738,11 +4738,11 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>03:19</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP28" t="n">
         <v>0.333</v>
@@ -4751,25 +4751,25 @@
         <v>0.333</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.075</v>
+        <v>0.15</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4778,71 +4778,71 @@
         <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#9 D. GIEDRAITIS (Per Game)</t>
+          <t>#10 A. TUBELIS (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5</v>
+        <v>17.25</v>
       </c>
       <c r="D29" t="n">
-        <v>0.25</v>
+        <v>5.25</v>
       </c>
       <c r="E29" t="n">
-        <v>0.25</v>
+        <v>8.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>-1</v>
+        <v>75</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -4857,139 +4857,139 @@
         <v>0.25</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>0.861</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0.25</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>0.25</v>
       </c>
-      <c r="AG29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>31:47</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>1</v>
+        <v>14.01</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.333</v>
+        <v>0.62</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.333</v>
+        <v>0.65</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.5</v>
+        <v>1.231</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.25</v>
+        <v>0.054</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>0.261</v>
       </c>
       <c r="AU29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>15.333</v>
       </c>
       <c r="AW29" t="n">
-        <v>5</v>
+        <v>16.333</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.046</v>
+        <v>0.219</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.019</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#10 A. TUBELIS (Per Game)</t>
+          <t>#12 M. LO (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>17.25</v>
+        <v>2.75</v>
       </c>
       <c r="D30" t="n">
-        <v>5.25</v>
+        <v>0.25</v>
       </c>
       <c r="E30" t="n">
-        <v>8.25</v>
+        <v>1.25</v>
       </c>
       <c r="F30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>1.25</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -5001,160 +5001,160 @@
         <v>0.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>0.75</v>
       </c>
       <c r="T30" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>7.75</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.861</v>
+        <v>0.5</v>
       </c>
       <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
+      <c r="AL30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM30" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0.444</v>
-      </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>60:32</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>14.01</v>
+        <v>4.44</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.62</v>
+        <v>0.308</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.65</v>
+        <v>0.373</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.231</v>
+        <v>0.619</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.054</v>
+        <v>0.169</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.261</v>
+        <v>0.231</v>
       </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="AV30" t="n">
-        <v>15.333</v>
+        <v>4.333</v>
       </c>
       <c r="AW30" t="n">
-        <v>16.333</v>
+        <v>5.667</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.115</v>
+        <v>0.15</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.059</v>
+        <v>0.044</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#12 M. LO (Per Game)</t>
+          <t>#14 D. SLEVA (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>2.75</v>
+        <v>4.25</v>
       </c>
       <c r="D31" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E31" t="n">
         <v>1.25</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
         <v>0.25</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -5163,220 +5163,220 @@
         <v>0.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
         <v>0.75</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
         <v>0.75</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.5</v>
       </c>
       <c r="AL31" t="n">
         <v>2</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>24:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>4.44</v>
+        <v>4.77</v>
       </c>
       <c r="AP31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="AT31" t="n">
         <v>0.308</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.231</v>
-      </c>
       <c r="AU31" t="n">
-        <v>1.333</v>
+        <v>0.667</v>
       </c>
       <c r="AV31" t="n">
         <v>4.333</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.667</v>
+        <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.089</v>
+        <v>0.151</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.012</v>
+        <v>0.076</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.026</v>
+        <v>0.083</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.038</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#14 D. SLEVA (Per Game)</t>
+          <t>#15 L. BIRUTIS (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="D32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F32" t="n">
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
         <v>0.75</v>
       </c>
-      <c r="G32" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="N32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.5</v>
       </c>
-      <c r="R32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.75</v>
-      </c>
       <c r="T32" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
         <v>1.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AC32" t="n">
         <v>0.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
@@ -5388,100 +5388,100 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>31:57</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>4.77</v>
+        <v>1.97</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.5</v>
+        <v>0.714</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.529</v>
+        <v>0.635</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.891</v>
+        <v>1.269</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.157</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.333</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.074</v>
+        <v>0.204</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.037</v>
+        <v>0.248</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.041</v>
+        <v>0.136</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#15 L. BIRUTIS (Per Game)</t>
+          <t>#51 A. BUTKEVICIUS (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H33" t="n">
         <v>1.25</v>
       </c>
-      <c r="E33" t="n">
+      <c r="I33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J33" t="n">
         <v>1.75</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
         <v>0.5</v>
@@ -5490,25 +5490,25 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5517,22 +5517,22 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
         <v>0.25</v>
       </c>
-      <c r="AC33" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AD33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -5547,127 +5547,127 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>1.97</v>
+        <v>3.3</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.714</v>
+        <v>0.167</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.635</v>
+        <v>0.357</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.269</v>
+        <v>0.606</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.134</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.164</v>
+        <v>0.078</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.09</v>
+        <v>0.103</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#51 A. BUTKEVICIUS (Per Game)</t>
+          <t>#91 D. SIRVYDIS (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F34" t="n">
         <v>0.25</v>
       </c>
       <c r="G34" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="H34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.25</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.5</v>
-      </c>
       <c r="S34" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="T34" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
@@ -5721,313 +5721,313 @@
         <v>0.25</v>
       </c>
       <c r="AL34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
         <v>1.5</v>
       </c>
-      <c r="AM34" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>41:36</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AP34" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.357</v>
+        <v>0.25</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.606</v>
+        <v>0.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.039</v>
+        <v>0.274</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.036</v>
+        <v>0.11</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.047</v>
+        <v>0.24</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#91 D. SIRVYDIS (Per Game)</t>
+          <t>#92 E. ULANOVAS (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>40</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC35" t="n">
         <v>0.75</v>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="AD35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0.25</v>
       </c>
-      <c r="F35" t="n">
+      <c r="AI35" t="n">
         <v>0.25</v>
       </c>
-      <c r="G35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
         <v>0.75</v>
       </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AL35" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>05:13</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>1.5</v>
+        <v>5.82</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.25</v>
+        <v>0.706</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.25</v>
+        <v>0.741</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.5</v>
+        <v>1.418</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.143</v>
+        <v>0.145</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.057</v>
+        <v>0.03</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.125</v>
+        <v>0.065</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#92 E. ULANOVAS (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="J36" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>1.25</v>
       </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.25</v>
-      </c>
       <c r="Q36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.929</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6039,228 +6039,228 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>43:46</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.741</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.418</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.529</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>80.75</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>34.25</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>3.5</v>
+        <v>18.75</v>
       </c>
       <c r="L37" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="R37" t="n">
+        <v>18</v>
+      </c>
+      <c r="S37" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="T37" t="n">
+        <v>384</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI37" t="n">
         <v>3</v>
       </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>206:15</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>82.97</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>0.508</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>0.973</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>1.727</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>5.523</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
@@ -6269,71 +6269,71 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>86.75</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>43.25</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>21.75</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>17.25</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T38" t="n">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -6342,422 +6342,92 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>0.848</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>18.25</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>206:15</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>1.25</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.036</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>1.408</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>5.306</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>6.714</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="D39" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="E39" t="n">
-        <v>34.25</v>
-      </c>
-      <c r="F39" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="G39" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>19</v>
-      </c>
-      <c r="I39" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>19</v>
-      </c>
-      <c r="K39" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="L39" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="M39" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="N39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="R39" t="n">
-        <v>18</v>
-      </c>
-      <c r="S39" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="T39" t="n">
-        <v>384</v>
-      </c>
-      <c r="U39" t="n">
-        <v>10</v>
-      </c>
-      <c r="V39" t="n">
-        <v>11</v>
-      </c>
-      <c r="W39" t="n">
-        <v>9</v>
-      </c>
-      <c r="X39" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>206:15</t>
-        </is>
-      </c>
-      <c r="AO39" t="n">
-        <v>82.97</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>1.727</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>5.523</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" t="n">
-        <v>86.75</v>
-      </c>
-      <c r="D40" t="n">
-        <v>24</v>
-      </c>
-      <c r="E40" t="n">
-        <v>43.25</v>
-      </c>
-      <c r="F40" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="G40" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H40" t="n">
-        <v>11</v>
-      </c>
-      <c r="I40" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="J40" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="K40" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="L40" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="R40" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="S40" t="n">
-        <v>20</v>
-      </c>
-      <c r="T40" t="n">
-        <v>404</v>
-      </c>
-      <c r="U40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="W40" t="n">
-        <v>5</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>206:15</t>
-        </is>
-      </c>
-      <c r="AO40" t="n">
-        <v>83.73999999999999</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1.408</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>5.306</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>6.714</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="BA40" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_ZALGIRIS KAUNAS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_ZALGIRIS KAUNAS.xlsx
@@ -671,13 +671,13 @@
         <v>0.3127572016460906</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="M2" t="n">
         <v>37</v>
@@ -752,13 +752,13 @@
         <v>0.8773584905660378</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.9387755102040817</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>1.761904761904762</v>
       </c>
       <c r="AN2" t="n">
         <v>1.727272727272727</v>
@@ -801,13 +801,13 @@
         <v>0.3127572016460906</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>9.25</v>
       </c>
       <c r="M3" t="n">
         <v>9.25</v>
@@ -882,13 +882,13 @@
         <v>0.8773584905660378</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.9387755102040817</v>
       </c>
       <c r="AM3" t="n">
-        <v>2</v>
+        <v>1.761904761904762</v>
       </c>
       <c r="AN3" t="n">
         <v>1.727272727272727</v>
@@ -931,13 +931,13 @@
         <v>0.1692307692307692</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
         <v>47</v>
@@ -1012,13 +1012,13 @@
         <v>1.275862068965517</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0392156862745098</v>
+        <v>1.215686274509804</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="AN4" t="n">
         <v>1.408163265306122</v>
@@ -1061,13 +1061,13 @@
         <v>0.1692307692307692</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>15.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M5" t="n">
         <v>11.75</v>
@@ -1142,13 +1142,13 @@
         <v>1.275862068965517</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0392156862745098</v>
+        <v>1.215686274509804</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="AN5" t="n">
         <v>1.408163265306122</v>
@@ -1486,16 +1486,16 @@
         <v>52</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="n">
         <v>16</v>
@@ -1651,16 +1651,16 @@
         <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
         <v>24</v>
@@ -1816,16 +1816,16 @@
         <v>68</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
         <v>27</v>
@@ -2152,10 +2152,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2311,16 +2311,16 @@
         <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
         <v>31</v>
@@ -2476,16 +2476,16 @@
         <v>5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>4</v>
@@ -2644,13 +2644,13 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>5</v>
@@ -2806,10 +2806,10 @@
         <v>16</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3301,16 +3301,16 @@
         <v>40</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
         <v>13</v>
@@ -3631,16 +3631,16 @@
         <v>384</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="W21" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="n">
         <v>130</v>
@@ -3796,16 +3796,16 @@
         <v>404</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V22" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="n">
         <v>106</v>
@@ -4020,16 +4020,16 @@
         <v>52</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Y24" t="n">
         <v>4</v>
@@ -4185,16 +4185,16 @@
         <v>78</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Y25" t="n">
         <v>6</v>
@@ -4350,16 +4350,16 @@
         <v>68</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="Y26" t="n">
         <v>6.75</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -4845,16 +4845,16 @@
         <v>75</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="W29" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="X29" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="Y29" t="n">
         <v>7.75</v>
@@ -5010,16 +5010,16 @@
         <v>5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Y30" t="n">
         <v>1</v>
@@ -5178,13 +5178,13 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Y31" t="n">
         <v>1.25</v>
@@ -5340,10 +5340,10 @@
         <v>16</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -5835,16 +5835,16 @@
         <v>40</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
         <v>3.25</v>
@@ -6165,16 +6165,16 @@
         <v>384</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>9.25</v>
       </c>
       <c r="X37" t="n">
-        <v>0.5</v>
+        <v>5.25</v>
       </c>
       <c r="Y37" t="n">
         <v>32.5</v>
@@ -6330,16 +6330,16 @@
         <v>404</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0.5</v>
+        <v>15.5</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y38" t="n">
         <v>26.5</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_ZALGIRIS KAUNAS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_ZALGIRIS KAUNAS.xlsx
@@ -683,13 +683,13 @@
         <v>37</v>
       </c>
       <c r="N2" t="n">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="O2" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6378600823045267</v>
+        <v>0.3251028806584362</v>
       </c>
       <c r="Q2" t="n">
         <v>20</v>
@@ -710,25 +710,25 @@
         <v>0.05349794238683128</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04938271604938271</v>
+        <v>0.06172839506172839</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3868312757201646</v>
+        <v>0.3744855967078189</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.6835443037974683</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4444444444444444</v>
@@ -737,13 +737,13 @@
         <v>0.2307692307692308</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2978723404255319</v>
+        <v>0.2747252747252747</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67741935483871</v>
+        <v>1.367088607594937</v>
       </c>
       <c r="AI2" t="n">
         <v>0.4615384615384616</v>
@@ -813,13 +813,13 @@
         <v>9.25</v>
       </c>
       <c r="N3" t="n">
-        <v>32.5</v>
+        <v>13.5</v>
       </c>
       <c r="O3" t="n">
-        <v>38.75</v>
+        <v>19.75</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6378600823045267</v>
+        <v>0.3251028806584362</v>
       </c>
       <c r="Q3" t="n">
         <v>5</v>
@@ -840,25 +840,25 @@
         <v>0.05349794238683128</v>
       </c>
       <c r="W3" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04938271604938271</v>
+        <v>0.06172839506172839</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.5</v>
+        <v>22.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3868312757201646</v>
+        <v>0.3744855967078189</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.6835443037974683</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4444444444444444</v>
@@ -867,13 +867,13 @@
         <v>0.2307692307692308</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.2978723404255319</v>
+        <v>0.2747252747252747</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.67741935483871</v>
+        <v>1.367088607594937</v>
       </c>
       <c r="AI3" t="n">
         <v>0.4615384615384616</v>
@@ -943,13 +943,13 @@
         <v>47</v>
       </c>
       <c r="N4" t="n">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="O4" t="n">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4807692307692308</v>
+        <v>0.3115384615384615</v>
       </c>
       <c r="Q4" t="n">
         <v>31</v>
@@ -970,25 +970,25 @@
         <v>0.06538461538461539</v>
       </c>
       <c r="W4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.06538461538461539</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2807692307692308</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.848</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4133333333333333</v>
@@ -997,13 +997,13 @@
         <v>0.1764705882352941</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.696</v>
+        <v>1.530864197530864</v>
       </c>
       <c r="AI4" t="n">
         <v>0.3529411764705883</v>
@@ -1073,13 +1073,13 @@
         <v>11.75</v>
       </c>
       <c r="N5" t="n">
-        <v>26.5</v>
+        <v>15.5</v>
       </c>
       <c r="O5" t="n">
-        <v>31.25</v>
+        <v>20.25</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4807692307692308</v>
+        <v>0.3115384615384615</v>
       </c>
       <c r="Q5" t="n">
         <v>7.75</v>
@@ -1100,25 +1100,25 @@
         <v>0.06538461538461539</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.06538461538461539</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.25</v>
+        <v>17.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2807692307692308</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.848</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4133333333333333</v>
@@ -1127,13 +1127,13 @@
         <v>0.1764705882352941</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.696</v>
+        <v>1.530864197530864</v>
       </c>
       <c r="AI5" t="n">
         <v>0.3529411764705883</v>
@@ -1498,13 +1498,13 @@
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.762</v>
+        <v>0.444</v>
       </c>
       <c r="AB8" t="n">
         <v>10</v>
@@ -1663,13 +1663,13 @@
         <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.889</v>
+        <v>0.625</v>
       </c>
       <c r="AB9" t="n">
         <v>1</v>
@@ -1690,22 +1690,22 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.303</v>
+        <v>0.281</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.844</v>
+        <v>0.75</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
@@ -2323,13 +2323,13 @@
         <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.861</v>
+        <v>0.792</v>
       </c>
       <c r="AB13" t="n">
         <v>2</v>
@@ -2350,22 +2350,22 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.444</v>
+        <v>0.375</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2653,10 +2653,10 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
         <v>1</v>
@@ -2680,22 +2680,22 @@
         <v>0.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.375</v>
+        <v>0.286</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3313,13 +3313,13 @@
         <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.929</v>
+        <v>0.8</v>
       </c>
       <c r="AB19" t="n">
         <v>2</v>
@@ -3643,13 +3643,13 @@
         <v>21</v>
       </c>
       <c r="Y21" t="n">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="Z21" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.839</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB21" t="n">
         <v>20</v>
@@ -3670,22 +3670,22 @@
         <v>0.231</v>
       </c>
       <c r="AH21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.298</v>
+        <v>0.275</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -3808,13 +3808,13 @@
         <v>15</v>
       </c>
       <c r="Y22" t="n">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="Z22" t="n">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.848</v>
+        <v>0.765</v>
       </c>
       <c r="AB22" t="n">
         <v>31</v>
@@ -3835,22 +3835,22 @@
         <v>0.176</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.714</v>
+        <v>0.647</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL22" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -4032,13 +4032,13 @@
         <v>0.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.25</v>
+        <v>2.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.762</v>
+        <v>0.444</v>
       </c>
       <c r="AB24" t="n">
         <v>2.5</v>
@@ -4197,13 +4197,13 @@
         <v>0.75</v>
       </c>
       <c r="Y25" t="n">
-        <v>6</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.75</v>
+        <v>2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.889</v>
+        <v>0.625</v>
       </c>
       <c r="AB25" t="n">
         <v>0.25</v>
@@ -4224,22 +4224,22 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AL25" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.303</v>
+        <v>0.281</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
@@ -4362,13 +4362,13 @@
         <v>1.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.75</v>
+        <v>3.75</v>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.844</v>
+        <v>0.75</v>
       </c>
       <c r="AB26" t="n">
         <v>1</v>
@@ -4857,13 +4857,13 @@
         <v>0.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.75</v>
+        <v>4.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.861</v>
+        <v>0.792</v>
       </c>
       <c r="AB29" t="n">
         <v>0.5</v>
@@ -4884,22 +4884,22 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.444</v>
+        <v>0.375</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5022,13 +5022,13 @@
         <v>0.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -5187,10 +5187,10 @@
         <v>0.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="AA31" t="n">
         <v>1</v>
@@ -5214,22 +5214,22 @@
         <v>0.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.375</v>
+        <v>0.286</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5847,13 +5847,13 @@
         <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.929</v>
+        <v>0.8</v>
       </c>
       <c r="AB35" t="n">
         <v>0.5</v>
@@ -6177,13 +6177,13 @@
         <v>5.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>32.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>38.75</v>
+        <v>19.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.839</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB37" t="n">
         <v>5</v>
@@ -6204,22 +6204,22 @@
         <v>0.231</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AK37" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AL37" t="n">
-        <v>23.5</v>
+        <v>22.75</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.298</v>
+        <v>0.275</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6342,13 +6342,13 @@
         <v>3.75</v>
       </c>
       <c r="Y38" t="n">
-        <v>26.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>31.25</v>
+        <v>20.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.848</v>
+        <v>0.765</v>
       </c>
       <c r="AB38" t="n">
         <v>7.75</v>
@@ -6369,22 +6369,22 @@
         <v>0.176</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.714</v>
+        <v>0.647</v>
       </c>
       <c r="AK38" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>18.25</v>
+        <v>17.5</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
